--- a/artfynd/A 41666-2024 artfynd.xlsx
+++ b/artfynd/A 41666-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>120746598</v>
       </c>
       <c r="B2" t="n">
-        <v>95606</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120746937</v>
+        <v>120745549</v>
       </c>
       <c r="B3" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595474</v>
+        <v>595433</v>
       </c>
       <c r="R3" t="n">
-        <v>7034733</v>
+        <v>7034767</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120747022</v>
+        <v>120745817</v>
       </c>
       <c r="B4" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595474</v>
+        <v>595438</v>
       </c>
       <c r="R4" t="n">
-        <v>7034758</v>
+        <v>7034712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120746170</v>
+        <v>120746663</v>
       </c>
       <c r="B5" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595445</v>
+        <v>595476</v>
       </c>
       <c r="R5" t="n">
-        <v>7034719</v>
+        <v>7034705</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120746207</v>
+        <v>120746937</v>
       </c>
       <c r="B6" t="n">
-        <v>91122</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595438</v>
+        <v>595474</v>
       </c>
       <c r="R6" t="n">
-        <v>7034706</v>
+        <v>7034733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120745549</v>
+        <v>120746170</v>
       </c>
       <c r="B7" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595433</v>
+        <v>595445</v>
       </c>
       <c r="R7" t="n">
-        <v>7034767</v>
+        <v>7034719</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120746663</v>
+        <v>120746207</v>
       </c>
       <c r="B8" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595476</v>
+        <v>595438</v>
       </c>
       <c r="R8" t="n">
-        <v>7034705</v>
+        <v>7034706</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120745413</v>
+        <v>120746359</v>
       </c>
       <c r="B9" t="n">
-        <v>90700</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595444</v>
+        <v>595456</v>
       </c>
       <c r="R9" t="n">
-        <v>7034736</v>
+        <v>7034709</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120745817</v>
+        <v>120746793</v>
       </c>
       <c r="B10" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595438</v>
+        <v>595483</v>
       </c>
       <c r="R10" t="n">
-        <v>7034712</v>
+        <v>7034699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120746359</v>
+        <v>120747022</v>
       </c>
       <c r="B11" t="n">
-        <v>91122</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595456</v>
+        <v>595474</v>
       </c>
       <c r="R11" t="n">
-        <v>7034709</v>
+        <v>7034758</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,12 +1648,7 @@
         <v>120746372</v>
       </c>
       <c r="B12" t="n">
-        <v>97013</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41666-2024 artfynd.xlsx
+++ b/artfynd/A 41666-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120745549</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120745817</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746663</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746937</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746170</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746207</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746793</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120747022</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>